--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N84_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N84_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>69.55117148999334</v>
+        <v>11.30206536712392</v>
       </c>
       <c r="D2" t="n">
-        <v>68.65898918064819</v>
+        <v>11.15708574185533</v>
       </c>
       <c r="E2" t="n">
-        <v>23.50296380136216</v>
+        <v>3.819231617721351</v>
       </c>
       <c r="F2" t="n">
-        <v>14.05519625236293</v>
+        <v>2.283969391008976</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>15.89379924842922</v>
+        <v>2.582742377869748</v>
       </c>
       <c r="D3" t="n">
-        <v>39.19093191530059</v>
+        <v>6.368526436236346</v>
       </c>
       <c r="E3" t="n">
-        <v>23.50296380136216</v>
+        <v>3.819231617721351</v>
       </c>
       <c r="F3" t="n">
-        <v>14.05519625236293</v>
+        <v>2.283969391008976</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>58.14614984485087</v>
+        <v>9.448749349788267</v>
       </c>
       <c r="D4" t="n">
-        <v>58.73070916435935</v>
+        <v>9.543740239208395</v>
       </c>
       <c r="E4" t="n">
-        <v>23.50296380136216</v>
+        <v>3.819231617721351</v>
       </c>
       <c r="F4" t="n">
-        <v>14.05519625236293</v>
+        <v>2.283969391008976</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>76.4155890240652</v>
+        <v>12.41753321641059</v>
       </c>
       <c r="D5" t="n">
-        <v>76.83772388494542</v>
+        <v>12.48613013130363</v>
       </c>
       <c r="E5" t="n">
-        <v>23.50296380136216</v>
+        <v>3.819231617721351</v>
       </c>
       <c r="F5" t="n">
-        <v>14.05519625236293</v>
+        <v>2.283969391008976</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
